--- a/reports/二级子公司C_利润表_2025-12.xlsx
+++ b/reports/二级子公司C_利润表_2025-12.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>85846596</v>
+        <v>87028688</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>83380562</v>
+        <v>82601729</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1036444561</v>
+        <v>1035338499</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>385888</v>
+        <v>390315</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>4837761</v>
+        <v>4840719</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>338166</v>
+        <v>341258</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>4231653</v>
+        <v>4237310</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>290498</v>
+        <v>292013</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>3626446</v>
+        <v>3633073</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>271813</v>
+        <v>271917</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>3384626</v>
+        <v>3391384</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>145959</v>
+        <v>145304</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1813478</v>
+        <v>1816769</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>116979</v>
+        <v>115978</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1451229</v>
+        <v>1453133</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>84297293</v>
+        <v>85471903</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>81831259</v>
+        <v>81044944</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>77963924</v>
+        <v>77162036</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>968641092</v>
+        <v>967630614</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1167192</v>
+        <v>1158981</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>14533319</v>
+        <v>14509371</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>776242</v>
+        <v>774276</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>9689787</v>
+        <v>9670767</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2903676</v>
+        <v>2910757</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>36333638</v>
+        <v>36263432</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>386341</v>
+        <v>389046</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4843288</v>
+        <v>4835722</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>289363</v>
+        <v>292355</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>3631135</v>
+        <v>3627803</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>482097</v>
+        <v>487813</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>6049339</v>
+        <v>6048674</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>578919</v>
+        <v>585446</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>7256282</v>
+        <v>7261487</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2416104</v>
+        <v>2437125</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>30225057</v>
+        <v>30267929</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>49930</v>
+        <v>50160</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>599331</v>
+        <v>600596</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1164973</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>14534609</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>774701</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>9689278</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>58284906</v>
+        <v>61839171</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>51897680</v>
+        <v>51294995</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>50728475</v>
+        <v>50137421</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>629416882</v>
+        <v>629186853</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1169205</v>
+        <v>1157574</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>14530225</v>
+        <v>14513702</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1932103</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>24181364</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>619618</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>7736481</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>388232</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>4835155</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>466994</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>5803034</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>350898</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>4353567</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>234168</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2903525</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>195136</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2420629</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>870036</v>
+        <v>877195</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>10880677</v>
+        <v>10896945</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>678275</v>
+        <v>680975</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>8461519</v>
+        <v>8477653</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>582843</v>
+        <v>582291</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>7252956</v>
+        <v>7267332</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4381188</v>
+        <v>4356289</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>54408149</v>
+        <v>54501125</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>201063</v>
+        <v>193197</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2398872</v>
+        <v>2421700</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>352096</v>
+        <v>348055</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>4199979</v>
+        <v>4201553</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>402243</v>
+        <v>348055</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4802213</v>
+        <v>4201553</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>50212</v>
+        <v>49731</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>600507</v>
+        <v>599665</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>179313</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>2158025</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>338963</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>4230827</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>120112</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1438402</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>90295</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1079011</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>150758</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1798992</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>487879</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>6049351</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>80462</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>960355</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>60276</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>720558</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>100261</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1201257</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>70011</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>840953</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>49884</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>600613</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>39825</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>480350</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>29830</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>360112</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>26012387</v>
+        <v>24839963</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>30474439</v>
+        <v>28029233</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>193311</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2417970</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>49937</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>599326</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>79753</v>
+        <v>80101</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>960903</v>
+        <v>958948</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>25932634</v>
+        <v>24953173</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2783490</v>
+        <v>2814634</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>33604991</v>
+        <v>33583118</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>23149144</v>
+        <v>22138539</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>23149144</v>
+        <v>22138539</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>23149144</v>
+        <v>22138539</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>23149144</v>
+        <v>22138539</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>23149144</v>
+        <v>22138539</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
